--- a/backend/data/financials_by_company/1420.HK.xlsx
+++ b/backend/data/financials_by_company/1420.HK.xlsx
@@ -647,548 +647,548 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>347416.57754</v>
+        <v>220374.120195</v>
       </c>
       <c r="C2" t="n">
-        <v>0.274421</v>
+        <v>0.187872</v>
       </c>
       <c r="D2" t="n">
-        <v>20270000</v>
+        <v>10342000</v>
       </c>
       <c r="E2" t="n">
-        <v>1266000</v>
+        <v>1173000</v>
       </c>
       <c r="F2" t="n">
-        <v>1266000</v>
+        <v>1173000</v>
       </c>
       <c r="G2" t="n">
-        <v>8141000</v>
+        <v>1500000</v>
       </c>
       <c r="H2" t="n">
-        <v>8356000</v>
+        <v>9229000</v>
       </c>
       <c r="I2" t="n">
-        <v>124791000</v>
+        <v>81079000</v>
       </c>
       <c r="J2" t="n">
-        <v>21536000</v>
+        <v>11515000</v>
       </c>
       <c r="K2" t="n">
-        <v>13180000</v>
+        <v>2286000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1639000</v>
+        <v>-392000</v>
       </c>
       <c r="M2" t="n">
-        <v>1960000</v>
+        <v>439000</v>
       </c>
       <c r="N2" t="n">
-        <v>321000</v>
+        <v>47000</v>
       </c>
       <c r="O2" t="n">
-        <v>7222416.57754</v>
+        <v>547374.120195</v>
       </c>
       <c r="P2" t="n">
-        <v>8141000</v>
+        <v>1500000</v>
       </c>
       <c r="Q2" t="n">
-        <v>131711000</v>
+        <v>85337000</v>
       </c>
       <c r="R2" t="n">
-        <v>1342651200</v>
+        <v>1153846154</v>
       </c>
       <c r="S2" t="n">
-        <v>1263427200</v>
+        <v>1036456000</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0061</v>
+        <v>0.0013</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0064</v>
+        <v>0.0014</v>
       </c>
       <c r="V2" t="n">
-        <v>8141000</v>
+        <v>1500000</v>
       </c>
       <c r="W2" t="n">
-        <v>8141000</v>
+        <v>1500000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>8141000</v>
+        <v>1500000</v>
       </c>
       <c r="Z2" t="n">
-        <v>8141000</v>
+        <v>1500000</v>
       </c>
       <c r="AA2" t="n">
-        <v>8141000</v>
+        <v>1500000</v>
       </c>
       <c r="AB2" t="n">
-        <v>3079000</v>
+        <v>347000</v>
       </c>
       <c r="AC2" t="n">
-        <v>11220000</v>
+        <v>1847000</v>
       </c>
       <c r="AD2" t="n">
-        <v>7000</v>
+        <v>404000</v>
       </c>
       <c r="AE2" t="n">
-        <v>779000</v>
+        <v>738000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-779000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>-467000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-271000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>-1639000</v>
+        <v>-392000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1960000</v>
+        <v>439000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>321000</v>
+        <v>47000</v>
       </c>
       <c r="AK2" t="n">
-        <v>12039000</v>
+        <v>79000</v>
       </c>
       <c r="AL2" t="n">
-        <v>6920000</v>
+        <v>4258000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-298000</v>
+        <v>-271000</v>
       </c>
       <c r="AN2" t="n">
-        <v>7732000</v>
+        <v>5835000</v>
       </c>
       <c r="AO2" t="n">
-        <v>7732000</v>
+        <v>5835000</v>
       </c>
       <c r="AP2" t="n">
-        <v>18959000</v>
+        <v>4337000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>124791000</v>
+        <v>81079000</v>
       </c>
       <c r="AR2" t="n">
-        <v>143750000</v>
+        <v>85416000</v>
       </c>
       <c r="AS2" t="n">
-        <v>143750000</v>
+        <v>85416000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>690117.182357</v>
+        <v>252594.006568</v>
       </c>
       <c r="C3" t="n">
-        <v>0.287909</v>
+        <v>0.292693</v>
       </c>
       <c r="D3" t="n">
-        <v>8822000</v>
+        <v>9140000</v>
       </c>
       <c r="E3" t="n">
-        <v>2397000</v>
+        <v>863000</v>
       </c>
       <c r="F3" t="n">
-        <v>2397000</v>
+        <v>863000</v>
       </c>
       <c r="G3" t="n">
-        <v>3245000</v>
+        <v>1723000</v>
       </c>
       <c r="H3" t="n">
-        <v>6425000</v>
+        <v>7354000</v>
       </c>
       <c r="I3" t="n">
-        <v>112240000</v>
+        <v>82407000</v>
       </c>
       <c r="J3" t="n">
-        <v>11219000</v>
+        <v>10003000</v>
       </c>
       <c r="K3" t="n">
-        <v>4794000</v>
+        <v>2649000</v>
       </c>
       <c r="L3" t="n">
-        <v>-44000</v>
+        <v>-156000</v>
       </c>
       <c r="M3" t="n">
-        <v>237000</v>
+        <v>213000</v>
       </c>
       <c r="N3" t="n">
-        <v>193000</v>
+        <v>57000</v>
       </c>
       <c r="O3" t="n">
-        <v>1538117.182357</v>
+        <v>1112594.006568</v>
       </c>
       <c r="P3" t="n">
-        <v>3245000</v>
+        <v>1723000</v>
       </c>
       <c r="Q3" t="n">
-        <v>118533000</v>
+        <v>87812000</v>
       </c>
       <c r="R3" t="n">
-        <v>1136408000</v>
+        <v>1148666667</v>
       </c>
       <c r="S3" t="n">
         <v>1036456000</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0029</v>
+        <v>0.0015</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0031</v>
+        <v>0.0017</v>
       </c>
       <c r="V3" t="n">
-        <v>3245000</v>
+        <v>1723000</v>
       </c>
       <c r="W3" t="n">
-        <v>3245000</v>
+        <v>1723000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>3245000</v>
+        <v>1723000</v>
       </c>
       <c r="Z3" t="n">
-        <v>3245000</v>
+        <v>1723000</v>
       </c>
       <c r="AA3" t="n">
-        <v>3245000</v>
+        <v>1723000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1312000</v>
+        <v>713000</v>
       </c>
       <c r="AC3" t="n">
-        <v>4557000</v>
+        <v>2436000</v>
       </c>
       <c r="AD3" t="n">
-        <v>486000</v>
+        <v>305000</v>
       </c>
       <c r="AE3" t="n">
-        <v>587000</v>
+        <v>520000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-587000</v>
+        <v>-202000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-47000</v>
+        <v>-318000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-44000</v>
+        <v>-156000</v>
       </c>
       <c r="AI3" t="n">
-        <v>237000</v>
+        <v>213000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>193000</v>
+        <v>57000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2299000</v>
+        <v>793000</v>
       </c>
       <c r="AL3" t="n">
-        <v>6293000</v>
+        <v>5405000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-47000</v>
+        <v>-318000</v>
       </c>
       <c r="AN3" t="n">
-        <v>6990000</v>
+        <v>6423000</v>
       </c>
       <c r="AO3" t="n">
-        <v>6990000</v>
+        <v>6423000</v>
       </c>
       <c r="AP3" t="n">
-        <v>8592000</v>
+        <v>6198000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>112240000</v>
+        <v>82407000</v>
       </c>
       <c r="AR3" t="n">
-        <v>120832000</v>
+        <v>88605000</v>
       </c>
       <c r="AS3" t="n">
-        <v>120832000</v>
+        <v>88605000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>252594.006568</v>
+        <v>690117.182357</v>
       </c>
       <c r="C4" t="n">
-        <v>0.292693</v>
+        <v>0.287909</v>
       </c>
       <c r="D4" t="n">
-        <v>9140000</v>
+        <v>8822000</v>
       </c>
       <c r="E4" t="n">
-        <v>863000</v>
+        <v>2397000</v>
       </c>
       <c r="F4" t="n">
-        <v>863000</v>
+        <v>2397000</v>
       </c>
       <c r="G4" t="n">
-        <v>1723000</v>
+        <v>3245000</v>
       </c>
       <c r="H4" t="n">
-        <v>7354000</v>
+        <v>6425000</v>
       </c>
       <c r="I4" t="n">
-        <v>82407000</v>
+        <v>112240000</v>
       </c>
       <c r="J4" t="n">
-        <v>10003000</v>
+        <v>11219000</v>
       </c>
       <c r="K4" t="n">
-        <v>2649000</v>
+        <v>4794000</v>
       </c>
       <c r="L4" t="n">
-        <v>-156000</v>
+        <v>-44000</v>
       </c>
       <c r="M4" t="n">
-        <v>213000</v>
+        <v>237000</v>
       </c>
       <c r="N4" t="n">
-        <v>57000</v>
+        <v>193000</v>
       </c>
       <c r="O4" t="n">
-        <v>1112594.006568</v>
+        <v>1538117.182357</v>
       </c>
       <c r="P4" t="n">
-        <v>1723000</v>
+        <v>3245000</v>
       </c>
       <c r="Q4" t="n">
-        <v>87812000</v>
+        <v>118533000</v>
       </c>
       <c r="R4" t="n">
-        <v>1148666667</v>
+        <v>1136408000</v>
       </c>
       <c r="S4" t="n">
         <v>1036456000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0015</v>
+        <v>0.0029</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="V4" t="n">
-        <v>1723000</v>
+        <v>3245000</v>
       </c>
       <c r="W4" t="n">
-        <v>1723000</v>
+        <v>3245000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1723000</v>
+        <v>3245000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1723000</v>
+        <v>3245000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1723000</v>
+        <v>3245000</v>
       </c>
       <c r="AB4" t="n">
-        <v>713000</v>
+        <v>1312000</v>
       </c>
       <c r="AC4" t="n">
-        <v>2436000</v>
+        <v>4557000</v>
       </c>
       <c r="AD4" t="n">
-        <v>305000</v>
+        <v>486000</v>
       </c>
       <c r="AE4" t="n">
-        <v>520000</v>
+        <v>587000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-202000</v>
+        <v>-587000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-318000</v>
+        <v>-47000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-156000</v>
+        <v>-44000</v>
       </c>
       <c r="AI4" t="n">
-        <v>213000</v>
+        <v>237000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>57000</v>
+        <v>193000</v>
       </c>
       <c r="AK4" t="n">
-        <v>793000</v>
+        <v>2299000</v>
       </c>
       <c r="AL4" t="n">
-        <v>5405000</v>
+        <v>6293000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-318000</v>
+        <v>-47000</v>
       </c>
       <c r="AN4" t="n">
-        <v>6423000</v>
+        <v>6990000</v>
       </c>
       <c r="AO4" t="n">
-        <v>6423000</v>
+        <v>6990000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6198000</v>
+        <v>8592000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>82407000</v>
+        <v>112240000</v>
       </c>
       <c r="AR4" t="n">
-        <v>88605000</v>
+        <v>120832000</v>
       </c>
       <c r="AS4" t="n">
-        <v>88605000</v>
+        <v>120832000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>220374.120195</v>
+        <v>347416.57754</v>
       </c>
       <c r="C5" t="n">
-        <v>0.187872</v>
+        <v>0.274421</v>
       </c>
       <c r="D5" t="n">
-        <v>10342000</v>
+        <v>20270000</v>
       </c>
       <c r="E5" t="n">
-        <v>1173000</v>
+        <v>1266000</v>
       </c>
       <c r="F5" t="n">
-        <v>1173000</v>
+        <v>1266000</v>
       </c>
       <c r="G5" t="n">
-        <v>1500000</v>
+        <v>8141000</v>
       </c>
       <c r="H5" t="n">
-        <v>9229000</v>
+        <v>8356000</v>
       </c>
       <c r="I5" t="n">
-        <v>81079000</v>
+        <v>124791000</v>
       </c>
       <c r="J5" t="n">
-        <v>11515000</v>
+        <v>21536000</v>
       </c>
       <c r="K5" t="n">
-        <v>2286000</v>
+        <v>13180000</v>
       </c>
       <c r="L5" t="n">
-        <v>-392000</v>
+        <v>-1639000</v>
       </c>
       <c r="M5" t="n">
-        <v>439000</v>
+        <v>1960000</v>
       </c>
       <c r="N5" t="n">
-        <v>47000</v>
+        <v>321000</v>
       </c>
       <c r="O5" t="n">
-        <v>547374.120195</v>
+        <v>7222416.57754</v>
       </c>
       <c r="P5" t="n">
-        <v>1500000</v>
+        <v>8141000</v>
       </c>
       <c r="Q5" t="n">
-        <v>85337000</v>
+        <v>131711000</v>
       </c>
       <c r="R5" t="n">
-        <v>1153846154</v>
+        <v>1342651200</v>
       </c>
       <c r="S5" t="n">
-        <v>1036456000</v>
+        <v>1263427200</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0013</v>
+        <v>0.0061</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0014</v>
+        <v>0.0064</v>
       </c>
       <c r="V5" t="n">
-        <v>1500000</v>
+        <v>8141000</v>
       </c>
       <c r="W5" t="n">
-        <v>1500000</v>
+        <v>8141000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1500000</v>
+        <v>8141000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1500000</v>
+        <v>8141000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1500000</v>
+        <v>8141000</v>
       </c>
       <c r="AB5" t="n">
-        <v>347000</v>
+        <v>3079000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1847000</v>
+        <v>11220000</v>
       </c>
       <c r="AD5" t="n">
-        <v>404000</v>
+        <v>7000</v>
       </c>
       <c r="AE5" t="n">
-        <v>738000</v>
+        <v>779000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-467000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-271000</v>
-      </c>
+        <v>-779000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-392000</v>
+        <v>-1639000</v>
       </c>
       <c r="AI5" t="n">
-        <v>439000</v>
+        <v>1960000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>47000</v>
+        <v>321000</v>
       </c>
       <c r="AK5" t="n">
-        <v>79000</v>
+        <v>12039000</v>
       </c>
       <c r="AL5" t="n">
-        <v>4258000</v>
+        <v>6920000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-271000</v>
+        <v>-298000</v>
       </c>
       <c r="AN5" t="n">
-        <v>5835000</v>
+        <v>7732000</v>
       </c>
       <c r="AO5" t="n">
-        <v>5835000</v>
+        <v>7732000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4337000</v>
+        <v>18959000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>81079000</v>
+        <v>124791000</v>
       </c>
       <c r="AR5" t="n">
-        <v>85416000</v>
+        <v>143750000</v>
       </c>
       <c r="AS5" t="n">
-        <v>85416000</v>
+        <v>143750000</v>
       </c>
     </row>
   </sheetData>
@@ -1544,203 +1544,203 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1263427200</v>
+        <v>1036456000</v>
       </c>
       <c r="D2" t="n">
-        <v>1263427200</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6125000</v>
-      </c>
+        <v>1036456000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>52101000</v>
+        <v>11425000</v>
       </c>
       <c r="G2" t="n">
-        <v>103148000</v>
+        <v>86507000</v>
       </c>
       <c r="H2" t="n">
-        <v>140681000</v>
+        <v>90803000</v>
       </c>
       <c r="I2" t="n">
-        <v>34046000</v>
+        <v>58940000</v>
       </c>
       <c r="J2" t="n">
-        <v>103148000</v>
+        <v>86507000</v>
       </c>
       <c r="K2" t="n">
-        <v>14568000</v>
+        <v>7129000</v>
       </c>
       <c r="L2" t="n">
-        <v>103148000</v>
+        <v>86507000</v>
       </c>
       <c r="M2" t="n">
-        <v>135312000</v>
+        <v>89576000</v>
       </c>
       <c r="N2" t="n">
-        <v>103148000</v>
+        <v>86507000</v>
       </c>
       <c r="O2" t="n">
-        <v>103148000</v>
+        <v>86507000</v>
       </c>
       <c r="P2" t="n">
-        <v>518000</v>
+        <v>521000</v>
       </c>
       <c r="Q2" t="n">
-        <v>65424000</v>
+        <v>52421000</v>
       </c>
       <c r="R2" t="n">
-        <v>29950000</v>
+        <v>27250000</v>
       </c>
       <c r="S2" t="n">
-        <v>2154000</v>
+        <v>1767000</v>
       </c>
       <c r="T2" t="n">
-        <v>2154000</v>
+        <v>1767000</v>
       </c>
       <c r="U2" t="n">
-        <v>88351000</v>
+        <v>25333000</v>
       </c>
       <c r="V2" t="n">
-        <v>37338000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+        <v>5732000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>7000</v>
+      </c>
       <c r="Y2" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>36838000</v>
+        <v>5725000</v>
       </c>
       <c r="AA2" t="n">
-        <v>4674000</v>
+        <v>2656000</v>
       </c>
       <c r="AB2" t="n">
-        <v>32164000</v>
+        <v>3069000</v>
       </c>
       <c r="AC2" t="n">
-        <v>51013000</v>
+        <v>19601000</v>
       </c>
       <c r="AD2" t="n">
-        <v>15263000</v>
+        <v>5700000</v>
       </c>
       <c r="AE2" t="n">
-        <v>9894000</v>
+        <v>4473000</v>
       </c>
       <c r="AF2" t="n">
-        <v>5369000</v>
+        <v>1227000</v>
       </c>
       <c r="AG2" t="n">
-        <v>14191000</v>
+        <v>7755000</v>
       </c>
       <c r="AH2" t="n">
-        <v>4077000</v>
+        <v>650000</v>
       </c>
       <c r="AI2" t="n">
-        <v>3353000</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6761000</v>
+        <v>7105000</v>
       </c>
       <c r="AK2" t="n">
-        <v>191499000</v>
+        <v>111840000</v>
       </c>
       <c r="AL2" t="n">
-        <v>106440000</v>
+        <v>33299000</v>
       </c>
       <c r="AM2" t="n">
-        <v>363000</v>
+        <v>369000</v>
       </c>
       <c r="AN2" t="n">
-        <v>620000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>138000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>411000</v>
+      </c>
       <c r="AP2" t="n">
-        <v>3813000</v>
+        <v>8279000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>535000</v>
+        <v>1175000</v>
       </c>
       <c r="AR2" t="n">
-        <v>3278000</v>
+        <v>7104000</v>
       </c>
       <c r="AS2" t="n">
-        <v>19460000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
+        <v>7587000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7587000</v>
+      </c>
       <c r="AU2" t="n">
-        <v>1262000</v>
+        <v>1298000</v>
       </c>
       <c r="AV2" t="n">
-        <v>80922000</v>
+        <v>15217000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-60492000</v>
+        <v>-52501000</v>
       </c>
       <c r="AX2" t="n">
-        <v>141414000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>389000</v>
-      </c>
+        <v>67718000</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>79149000</v>
+        <v>65791000</v>
       </c>
       <c r="BB2" t="n">
-        <v>61876000</v>
+        <v>1927000</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>85059000</v>
+        <v>78541000</v>
       </c>
       <c r="BE2" t="n">
-        <v>1290000</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="n">
-        <v>1638000</v>
-      </c>
+        <v>1276000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2919000</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="n">
-        <v>30606000</v>
+        <v>27015000</v>
       </c>
       <c r="BI2" t="n">
-        <v>17877000</v>
+        <v>18736000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-1294000</v>
+        <v>-1337000</v>
       </c>
       <c r="BK2" t="n">
-        <v>19171000</v>
+        <v>20073000</v>
       </c>
       <c r="BL2" t="n">
-        <v>33648000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>2240000</v>
-      </c>
+        <v>31514000</v>
+      </c>
+      <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="n">
-        <v>31408000</v>
+        <v>31514000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3823000</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>27585000</v>
+        <v>31514000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+        <v>44926</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>1036456000</v>
       </c>
@@ -1749,40 +1749,40 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>8738000</v>
+        <v>7151000</v>
       </c>
       <c r="G3" t="n">
-        <v>92088000</v>
+        <v>88783000</v>
       </c>
       <c r="H3" t="n">
-        <v>93905000</v>
+        <v>91852000</v>
       </c>
       <c r="I3" t="n">
-        <v>50396000</v>
+        <v>59387000</v>
       </c>
       <c r="J3" t="n">
-        <v>92088000</v>
+        <v>88783000</v>
       </c>
       <c r="K3" t="n">
-        <v>6921000</v>
+        <v>4082000</v>
       </c>
       <c r="L3" t="n">
-        <v>92088000</v>
+        <v>88783000</v>
       </c>
       <c r="M3" t="n">
-        <v>92628000</v>
+        <v>90600000</v>
       </c>
       <c r="N3" t="n">
-        <v>92088000</v>
+        <v>88783000</v>
       </c>
       <c r="O3" t="n">
-        <v>92088000</v>
+        <v>88783000</v>
       </c>
       <c r="P3" t="n">
-        <v>664000</v>
+        <v>604000</v>
       </c>
       <c r="Q3" t="n">
-        <v>57283000</v>
+        <v>54144000</v>
       </c>
       <c r="R3" t="n">
         <v>27250000</v>
@@ -1794,147 +1794,149 @@
         <v>1767000</v>
       </c>
       <c r="U3" t="n">
-        <v>29597000</v>
+        <v>21752000</v>
       </c>
       <c r="V3" t="n">
-        <v>3522000</v>
+        <v>3085000</v>
       </c>
       <c r="W3" t="n">
-        <v>11000</v>
+        <v>6000</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3455000</v>
+        <v>3079000</v>
       </c>
       <c r="AA3" t="n">
-        <v>2915000</v>
+        <v>1262000</v>
       </c>
       <c r="AB3" t="n">
-        <v>540000</v>
+        <v>1817000</v>
       </c>
       <c r="AC3" t="n">
-        <v>26075000</v>
+        <v>18667000</v>
       </c>
       <c r="AD3" t="n">
-        <v>5283000</v>
+        <v>4072000</v>
       </c>
       <c r="AE3" t="n">
-        <v>4006000</v>
+        <v>2820000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1277000</v>
+        <v>1252000</v>
       </c>
       <c r="AG3" t="n">
-        <v>12230000</v>
+        <v>8082000</v>
       </c>
       <c r="AH3" t="n">
-        <v>3157000</v>
+        <v>660000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1031000</v>
+        <v>529000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8042000</v>
+        <v>6893000</v>
       </c>
       <c r="AK3" t="n">
-        <v>121685000</v>
+        <v>110535000</v>
       </c>
       <c r="AL3" t="n">
-        <v>45214000</v>
+        <v>32481000</v>
       </c>
       <c r="AM3" t="n">
-        <v>366000</v>
+        <v>365000</v>
       </c>
       <c r="AN3" t="n">
-        <v>520000</v>
+        <v>140000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>228000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9306000</v>
+        <v>9518000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>807000</v>
+        <v>1644000</v>
       </c>
       <c r="AR3" t="n">
-        <v>8499000</v>
+        <v>7874000</v>
       </c>
       <c r="AS3" t="n">
-        <v>16928000</v>
+        <v>9924000</v>
       </c>
       <c r="AT3" t="n">
-        <v>16928000</v>
+        <v>9924000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1274000</v>
+        <v>1286000</v>
       </c>
       <c r="AV3" t="n">
-        <v>16820000</v>
+        <v>11020000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-58576000</v>
+        <v>-57063000</v>
       </c>
       <c r="AX3" t="n">
-        <v>75396000</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
+        <v>68083000</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>11020000</v>
+      </c>
       <c r="BA3" t="n">
-        <v>75396000</v>
+        <v>66670000</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1413000</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>76471000</v>
+        <v>78054000</v>
       </c>
       <c r="BE3" t="n">
-        <v>1285000</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
+        <v>1281000</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3460000</v>
+      </c>
+      <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
-        <v>29012000</v>
+        <v>31480000</v>
       </c>
       <c r="BI3" t="n">
-        <v>16069000</v>
+        <v>21852000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-1175000</v>
+        <v>-1044000</v>
       </c>
       <c r="BK3" t="n">
-        <v>17244000</v>
+        <v>22896000</v>
       </c>
       <c r="BL3" t="n">
-        <v>30105000</v>
+        <v>23441000</v>
       </c>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="n">
-        <v>30105000</v>
+        <v>23441000</v>
       </c>
       <c r="BO3" t="n">
-        <v>6685000</v>
+        <v>3000000</v>
       </c>
       <c r="BP3" t="n">
-        <v>23420000</v>
+        <v>20441000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
         <v>1036456000</v>
       </c>
@@ -1943,40 +1945,40 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>7151000</v>
+        <v>8738000</v>
       </c>
       <c r="G4" t="n">
-        <v>88783000</v>
+        <v>92088000</v>
       </c>
       <c r="H4" t="n">
-        <v>91852000</v>
+        <v>93905000</v>
       </c>
       <c r="I4" t="n">
-        <v>59387000</v>
+        <v>50396000</v>
       </c>
       <c r="J4" t="n">
-        <v>88783000</v>
+        <v>92088000</v>
       </c>
       <c r="K4" t="n">
-        <v>4082000</v>
+        <v>6921000</v>
       </c>
       <c r="L4" t="n">
-        <v>88783000</v>
+        <v>92088000</v>
       </c>
       <c r="M4" t="n">
-        <v>90600000</v>
+        <v>92628000</v>
       </c>
       <c r="N4" t="n">
-        <v>88783000</v>
+        <v>92088000</v>
       </c>
       <c r="O4" t="n">
-        <v>88783000</v>
+        <v>92088000</v>
       </c>
       <c r="P4" t="n">
-        <v>604000</v>
+        <v>664000</v>
       </c>
       <c r="Q4" t="n">
-        <v>54144000</v>
+        <v>57283000</v>
       </c>
       <c r="R4" t="n">
         <v>27250000</v>
@@ -1988,334 +1990,332 @@
         <v>1767000</v>
       </c>
       <c r="U4" t="n">
-        <v>21752000</v>
+        <v>29597000</v>
       </c>
       <c r="V4" t="n">
-        <v>3085000</v>
+        <v>3522000</v>
       </c>
       <c r="W4" t="n">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
+        <v>56000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3455000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2915000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>540000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>26075000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>5283000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>4006000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1277000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12230000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3157000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1031000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>8042000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>121685000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>45214000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>366000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>520000</v>
+      </c>
+      <c r="AO4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" t="n">
-        <v>3079000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1262000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1817000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>18667000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4072000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2820000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1252000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>8082000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>660000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>529000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>6893000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>110535000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>32481000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>365000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>140000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>228000</v>
-      </c>
       <c r="AP4" t="n">
-        <v>9518000</v>
+        <v>9306000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1644000</v>
+        <v>807000</v>
       </c>
       <c r="AR4" t="n">
-        <v>7874000</v>
+        <v>8499000</v>
       </c>
       <c r="AS4" t="n">
-        <v>9924000</v>
+        <v>16928000</v>
       </c>
       <c r="AT4" t="n">
-        <v>9924000</v>
+        <v>16928000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1286000</v>
+        <v>1274000</v>
       </c>
       <c r="AV4" t="n">
-        <v>11020000</v>
+        <v>16820000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-57063000</v>
+        <v>-58576000</v>
       </c>
       <c r="AX4" t="n">
-        <v>68083000</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="n">
-        <v>11020000</v>
-      </c>
+        <v>75396000</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>66670000</v>
+        <v>75396000</v>
       </c>
       <c r="BB4" t="n">
-        <v>1413000</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>78054000</v>
+        <v>76471000</v>
       </c>
       <c r="BE4" t="n">
-        <v>1281000</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3460000</v>
-      </c>
-      <c r="BG4" t="inlineStr"/>
+        <v>1285000</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
       <c r="BH4" t="n">
-        <v>31480000</v>
+        <v>29012000</v>
       </c>
       <c r="BI4" t="n">
-        <v>21852000</v>
+        <v>16069000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-1044000</v>
+        <v>-1175000</v>
       </c>
       <c r="BK4" t="n">
-        <v>22896000</v>
+        <v>17244000</v>
       </c>
       <c r="BL4" t="n">
-        <v>23441000</v>
+        <v>30105000</v>
       </c>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="n">
-        <v>23441000</v>
+        <v>30105000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3000000</v>
+        <v>6685000</v>
       </c>
       <c r="BP4" t="n">
-        <v>20441000</v>
+        <v>23420000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1036456000</v>
+        <v>1263427200</v>
       </c>
       <c r="D5" t="n">
-        <v>1036456000</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>1263427200</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6125000</v>
+      </c>
       <c r="F5" t="n">
-        <v>11425000</v>
+        <v>52101000</v>
       </c>
       <c r="G5" t="n">
-        <v>86507000</v>
+        <v>103148000</v>
       </c>
       <c r="H5" t="n">
-        <v>90803000</v>
+        <v>140681000</v>
       </c>
       <c r="I5" t="n">
-        <v>58940000</v>
+        <v>34046000</v>
       </c>
       <c r="J5" t="n">
-        <v>86507000</v>
+        <v>103148000</v>
       </c>
       <c r="K5" t="n">
-        <v>7129000</v>
+        <v>14568000</v>
       </c>
       <c r="L5" t="n">
-        <v>86507000</v>
+        <v>103148000</v>
       </c>
       <c r="M5" t="n">
-        <v>89576000</v>
+        <v>135312000</v>
       </c>
       <c r="N5" t="n">
-        <v>86507000</v>
+        <v>103148000</v>
       </c>
       <c r="O5" t="n">
-        <v>86507000</v>
+        <v>103148000</v>
       </c>
       <c r="P5" t="n">
-        <v>521000</v>
+        <v>518000</v>
       </c>
       <c r="Q5" t="n">
-        <v>52421000</v>
+        <v>65424000</v>
       </c>
       <c r="R5" t="n">
-        <v>27250000</v>
+        <v>29950000</v>
       </c>
       <c r="S5" t="n">
-        <v>1767000</v>
+        <v>2154000</v>
       </c>
       <c r="T5" t="n">
-        <v>1767000</v>
+        <v>2154000</v>
       </c>
       <c r="U5" t="n">
-        <v>25333000</v>
+        <v>88351000</v>
       </c>
       <c r="V5" t="n">
-        <v>5732000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>7000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>7000</v>
-      </c>
+        <v>37338000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="Z5" t="n">
-        <v>5725000</v>
+        <v>36838000</v>
       </c>
       <c r="AA5" t="n">
-        <v>2656000</v>
+        <v>4674000</v>
       </c>
       <c r="AB5" t="n">
-        <v>3069000</v>
+        <v>32164000</v>
       </c>
       <c r="AC5" t="n">
-        <v>19601000</v>
+        <v>51013000</v>
       </c>
       <c r="AD5" t="n">
-        <v>5700000</v>
+        <v>15263000</v>
       </c>
       <c r="AE5" t="n">
-        <v>4473000</v>
+        <v>9894000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1227000</v>
+        <v>5369000</v>
       </c>
       <c r="AG5" t="n">
-        <v>7755000</v>
+        <v>14191000</v>
       </c>
       <c r="AH5" t="n">
-        <v>650000</v>
+        <v>4077000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>3353000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>7105000</v>
+        <v>6761000</v>
       </c>
       <c r="AK5" t="n">
-        <v>111840000</v>
+        <v>191499000</v>
       </c>
       <c r="AL5" t="n">
-        <v>33299000</v>
+        <v>106440000</v>
       </c>
       <c r="AM5" t="n">
-        <v>369000</v>
+        <v>363000</v>
       </c>
       <c r="AN5" t="n">
-        <v>138000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>411000</v>
-      </c>
+        <v>620000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>8279000</v>
+        <v>3813000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1175000</v>
+        <v>535000</v>
       </c>
       <c r="AR5" t="n">
-        <v>7104000</v>
+        <v>3278000</v>
       </c>
       <c r="AS5" t="n">
-        <v>7587000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7587000</v>
-      </c>
+        <v>19460000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>1298000</v>
+        <v>1262000</v>
       </c>
       <c r="AV5" t="n">
-        <v>15217000</v>
+        <v>80922000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-52501000</v>
+        <v>-60492000</v>
       </c>
       <c r="AX5" t="n">
-        <v>67718000</v>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+        <v>141414000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>389000</v>
+      </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>65791000</v>
+        <v>79149000</v>
       </c>
       <c r="BB5" t="n">
-        <v>1927000</v>
+        <v>61876000</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>78541000</v>
+        <v>85059000</v>
       </c>
       <c r="BE5" t="n">
-        <v>1276000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2919000</v>
-      </c>
-      <c r="BG5" t="inlineStr"/>
+        <v>1290000</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="n">
+        <v>1638000</v>
+      </c>
       <c r="BH5" t="n">
-        <v>27015000</v>
+        <v>30606000</v>
       </c>
       <c r="BI5" t="n">
-        <v>18736000</v>
+        <v>17877000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-1337000</v>
+        <v>-1294000</v>
       </c>
       <c r="BK5" t="n">
-        <v>20073000</v>
+        <v>19171000</v>
       </c>
       <c r="BL5" t="n">
-        <v>31514000</v>
-      </c>
-      <c r="BM5" t="inlineStr"/>
+        <v>33648000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>2240000</v>
+      </c>
       <c r="BN5" t="n">
-        <v>31514000</v>
+        <v>31408000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>3823000</v>
       </c>
       <c r="BP5" t="n">
-        <v>31514000</v>
+        <v>27585000</v>
       </c>
     </row>
   </sheetData>
@@ -2566,552 +2566,552 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>25650000</v>
+        <v>1555000</v>
       </c>
       <c r="C2" t="n">
-        <v>-21831000</v>
+        <v>-704000</v>
       </c>
       <c r="D2" t="n">
-        <v>39720000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2941000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-3133000</v>
+        <v>-4069000</v>
       </c>
       <c r="G2" t="n">
-        <v>31408000</v>
+        <v>31514000</v>
       </c>
       <c r="H2" t="n">
-        <v>30105000</v>
+        <v>46238000</v>
       </c>
       <c r="I2" t="n">
-        <v>111000</v>
+        <v>612000</v>
       </c>
       <c r="J2" t="n">
-        <v>1192000</v>
+        <v>-15336000</v>
       </c>
       <c r="K2" t="n">
-        <v>15447000</v>
+        <v>-5893000</v>
       </c>
       <c r="L2" t="n">
-        <v>-5000</v>
+        <v>2116000</v>
       </c>
       <c r="M2" t="n">
-        <v>-1933000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2941000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2941000</v>
-      </c>
+        <v>-439000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>17889000</v>
+        <v>-704000</v>
       </c>
       <c r="Q2" t="n">
-        <v>17889000</v>
+        <v>-704000</v>
       </c>
       <c r="R2" t="n">
-        <v>-21831000</v>
+        <v>-704000</v>
       </c>
       <c r="S2" t="n">
-        <v>39720000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-43038000</v>
+        <v>-15067000</v>
       </c>
       <c r="U2" t="n">
-        <v>362000</v>
+        <v>32000</v>
       </c>
       <c r="V2" t="n">
-        <v>9000</v>
+        <v>28000</v>
       </c>
       <c r="W2" t="n">
-        <v>3468000</v>
+        <v>-4119000</v>
       </c>
       <c r="X2" t="n">
-        <v>3846000</v>
+        <v>1480000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-378000</v>
+        <v>-5599000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-44675000</v>
+        <v>-7577000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-44675000</v>
+        <v>-7577000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2202000</v>
+        <v>-3431000</v>
       </c>
       <c r="AC2" t="n">
-        <v>931000</v>
+        <v>638000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-3133000</v>
+        <v>-4069000</v>
       </c>
       <c r="AE2" t="n">
-        <v>28783000</v>
+        <v>5624000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1486000</v>
+        <v>-136000</v>
       </c>
       <c r="AG2" t="n">
-        <v>9526000</v>
+        <v>-4863000</v>
       </c>
       <c r="AH2" t="n">
-        <v>10692000</v>
+        <v>-1494000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1196000</v>
+        <v>-2752000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2029000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-1638000</v>
-      </c>
+        <v>715000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>-2753000</v>
+        <v>-1332000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1639000</v>
+        <v>379000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>361000</v>
       </c>
       <c r="AO2" t="n">
-        <v>88000</v>
+        <v>-264000</v>
       </c>
       <c r="AP2" t="n">
-        <v>8356000</v>
+        <v>9229000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8356000</v>
+        <v>9229000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-496000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-111000</v>
-      </c>
+        <v>-450000</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>-779000</v>
+        <v>-467000</v>
       </c>
       <c r="AU2" t="n">
-        <v>11220000</v>
+        <v>1847000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>16111000</v>
+        <v>-511000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1252000</v>
-      </c>
-      <c r="D3" t="n">
+        <v>-1227000</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>-1662000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23441000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>31514000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-8064000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-5921000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-213000</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>-1227000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-1227000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-1227000</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>-3294000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>41000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>46000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-427000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>910000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-1337000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-1752000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-1752000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-1202000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>460000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-1662000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1151000</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-6359000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>30105000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>23441000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-127000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6791000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-4645000</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="AG3" t="n">
+        <v>-7643000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-527000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>447000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-527000</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="n">
+        <v>-7036000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>88000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>83000</v>
+      </c>
+      <c r="AO3" t="n">
         <v>-4000</v>
       </c>
-      <c r="M3" t="n">
-        <v>-237000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-1252000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-1252000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-1252000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-11034000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>166000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>10000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2071000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3286000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-1215000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-7646000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-7646000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-5635000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>724000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-6359000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>22470000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-525000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13502000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1806000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>3893000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1402000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>6401000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>44000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>60000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>97000</v>
-      </c>
       <c r="AP3" t="n">
-        <v>6425000</v>
+        <v>7354000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6425000</v>
+        <v>7354000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1869000</v>
+        <v>-389000</v>
       </c>
       <c r="AS3" t="n">
-        <v>127000</v>
+        <v>9000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-587000</v>
+        <v>-202000</v>
       </c>
       <c r="AU3" t="n">
-        <v>4557000</v>
+        <v>2436000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-511000</v>
+        <v>16111000</v>
       </c>
       <c r="C4" t="n">
-        <v>-1227000</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+        <v>-1252000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
       <c r="F4" t="n">
-        <v>-1662000</v>
+        <v>-6359000</v>
       </c>
       <c r="G4" t="n">
+        <v>30105000</v>
+      </c>
+      <c r="H4" t="n">
         <v>23441000</v>
       </c>
-      <c r="H4" t="n">
-        <v>31514000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-9000</v>
+        <v>-127000</v>
       </c>
       <c r="J4" t="n">
-        <v>-8064000</v>
+        <v>6791000</v>
       </c>
       <c r="K4" t="n">
-        <v>-5921000</v>
+        <v>-4645000</v>
       </c>
       <c r="L4" t="n">
-        <v>-5000</v>
+        <v>-4000</v>
       </c>
       <c r="M4" t="n">
-        <v>-213000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+        <v>-237000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>-1227000</v>
+        <v>-1252000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1227000</v>
+        <v>-1252000</v>
       </c>
       <c r="R4" t="n">
-        <v>-1227000</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
+        <v>-1252000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
       <c r="T4" t="n">
-        <v>-3294000</v>
+        <v>-11034000</v>
       </c>
       <c r="U4" t="n">
-        <v>41000</v>
+        <v>166000</v>
       </c>
       <c r="V4" t="n">
-        <v>46000</v>
+        <v>10000</v>
       </c>
       <c r="W4" t="n">
-        <v>-427000</v>
+        <v>2071000</v>
       </c>
       <c r="X4" t="n">
-        <v>910000</v>
+        <v>3286000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1337000</v>
+        <v>-1215000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1752000</v>
+        <v>-7646000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1752000</v>
+        <v>-7646000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1202000</v>
+        <v>-5635000</v>
       </c>
       <c r="AC4" t="n">
-        <v>460000</v>
+        <v>724000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1662000</v>
+        <v>-6359000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1151000</v>
+        <v>22470000</v>
       </c>
       <c r="AF4" t="n">
+        <v>-525000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13502000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1806000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>3893000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1402000</v>
+      </c>
+      <c r="AK4" t="n">
         <v>0</v>
       </c>
-      <c r="AG4" t="n">
-        <v>-7643000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-527000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>447000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-527000</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-7036000</v>
+        <v>6401000</v>
       </c>
       <c r="AM4" t="n">
-        <v>88000</v>
+        <v>44000</v>
       </c>
       <c r="AN4" t="n">
-        <v>83000</v>
+        <v>60000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-4000</v>
+        <v>97000</v>
       </c>
       <c r="AP4" t="n">
-        <v>7354000</v>
+        <v>6425000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7354000</v>
+        <v>6425000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-389000</v>
+        <v>-1869000</v>
       </c>
       <c r="AS4" t="n">
-        <v>9000</v>
+        <v>127000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-202000</v>
+        <v>-587000</v>
       </c>
       <c r="AU4" t="n">
-        <v>2436000</v>
+        <v>4557000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1555000</v>
+        <v>25650000</v>
       </c>
       <c r="C5" t="n">
-        <v>-704000</v>
+        <v>-21831000</v>
       </c>
       <c r="D5" t="n">
+        <v>39720000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2941000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-3133000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>31408000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30105000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>111000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1192000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>15447000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-1933000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2941000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2941000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>17889000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>17889000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-21831000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>39720000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-43038000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>362000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>9000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3468000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3846000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-378000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-44675000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-44675000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-2202000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>931000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-3133000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>28783000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-1486000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9526000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>10692000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1196000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2029000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-1638000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-2753000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1639000</v>
+      </c>
+      <c r="AN5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>-4069000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>31514000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>46238000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>612000</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-15336000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-5893000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2116000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-439000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>-704000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-704000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-704000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-15067000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>32000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>28000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-4119000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1480000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-5599000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-7577000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-7577000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-3431000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>638000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-4069000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>5624000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-136000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-4863000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-1494000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-2752000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>715000</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="n">
-        <v>-1332000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>379000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>361000</v>
-      </c>
       <c r="AO5" t="n">
-        <v>-264000</v>
+        <v>88000</v>
       </c>
       <c r="AP5" t="n">
-        <v>9229000</v>
+        <v>8356000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9229000</v>
+        <v>8356000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-450000</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+        <v>-496000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-111000</v>
+      </c>
       <c r="AT5" t="n">
-        <v>-467000</v>
+        <v>-779000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1847000</v>
+        <v>11220000</v>
       </c>
     </row>
   </sheetData>
@@ -3641,187 +3641,187 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
         </is>
       </c>
       <c r="EJ1" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Yew Kiat  Phang', 'age': 57, 'title': 'Executive Chairman of the Board', 'yearBorn': 1968, 'fiscalYear': 2025, 'totalPay': 735235, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kui Teng  Lim', 'age': 56, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 7922157, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sok Hun  Ong', 'age': 51, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 1807453, 'exercisedValue': 0, 'unexercisedValue': 662680}, {'maxAge': 1, 'name': 'Mr. Bijay  Joseph', 'age': 56, 'title': 'Executive Director', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 2481418, 'exercisedValue': 0, 'unexercisedValue': 623694}, {'maxAge': 1, 'name': 'Mr. Kai Tak  Ho', 'age': 65, 'title': 'Company Secretary', 'yearBorn': 1960, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Yew Kiat  Phang', 'age': 57, 'title': 'Executive Chairman of the Board', 'yearBorn': 1968, 'fiscalYear': 2025, 'totalPay': 727579, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kui Teng  Lim', 'age': 56, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 7839665, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sok Hun  Ong', 'age': 51, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 1788632, 'exercisedValue': 0, 'unexercisedValue': 655779}, {'maxAge': 1, 'name': 'Mr. Bijay  Joseph', 'age': 56, 'title': 'Executive Director', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 2455580, 'exercisedValue': 0, 'unexercisedValue': 617199}, {'maxAge': 1, 'name': 'Mr. Kai Tak  Ho', 'age': 65, 'title': 'Company Secretary', 'yearBorn': 1960, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3924,58 +3924,58 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V2" t="n">
-        <v>0.202</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="n">
-        <v>0.202</v>
+        <v>0.2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.211</v>
+        <v>0.204</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.202</v>
+        <v>0.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.202</v>
+        <v>0.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.211</v>
+        <v>0.204</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.33</v>
+        <v>0.313</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.3333333</v>
+        <v>2.2666667</v>
       </c>
       <c r="AF2" t="n">
-        <v>284000</v>
+        <v>68000</v>
       </c>
       <c r="AG2" t="n">
-        <v>284000</v>
+        <v>68000</v>
       </c>
       <c r="AH2" t="n">
-        <v>567666</v>
+        <v>430644</v>
       </c>
       <c r="AI2" t="n">
-        <v>112444</v>
+        <v>188400</v>
       </c>
       <c r="AJ2" t="n">
-        <v>112444</v>
+        <v>188400</v>
       </c>
       <c r="AK2" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="AL2" t="n">
         <v>0.205</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.21</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -3984,13 +3984,13 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>281956736</v>
+        <v>273900832</v>
       </c>
       <c r="AP2" t="n">
-        <v>295383264</v>
+        <v>273900844</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.105</v>
+        <v>0.116</v>
       </c>
       <c r="AR2" t="n">
         <v>0.315</v>
@@ -4002,13 +4002,13 @@
         <v>0.045</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.65853</v>
+        <v>1.6111435</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.24176</v>
+        <v>0.22522</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.21243</v>
+        <v>0.215295</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>267847712</v>
+        <v>260267152</v>
       </c>
       <c r="BC2" t="n">
         <v>0.111549996</v>
@@ -4037,7 +4037,7 @@
         <v>1342651200</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.5936000299999999</v>
+        <v>0.59993</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -4046,10 +4046,10 @@
         <v>1342651200</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.5952083</v>
+        <v>0.5881265</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.35281765</v>
+        <v>0.34686416</v>
       </c>
       <c r="BK2" t="n">
         <v>1767139200</v>
@@ -4070,16 +4070,16 @@
         <v>0.09</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.576</v>
+        <v>1.531</v>
       </c>
       <c r="BR2" t="n">
-        <v>8.891</v>
+        <v>8.638999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.0952382</v>
+        <v>0.4890511</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>0.21</v>
+        <v>0.204</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -4189,140 +4189,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1465435800000</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>0.003999993</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>0.2 - 0.204</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>430644</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.7586207</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>0.116 - 0.315</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.111</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.35238096</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>48.90511</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1756551540</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1757160000</v>
+      </c>
+      <c r="DN2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.021219999</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.09421898400000001</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.011295006</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.052462924</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DV2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>finmb_339911352</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DC2" t="n">
+      <c r="DZ2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DE2" t="b">
+      <c r="EB2" t="b">
         <v>0</v>
       </c>
-      <c r="DF2" t="n">
-        <v>-4.545457</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DH2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>CHUAN HOLDING</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>Chuan Holdings Limited</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DI2" t="n">
-        <v>1780381317</v>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>1465435800000</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.010000005</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>0.202 - 0.211</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>567666</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>Chuan Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>CHUAN HOLDING</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DU2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.031760007</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.13136998</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.0024300069</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.011439094</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>0.105 - 0.315</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.105000004</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.33333334</v>
-      </c>
       <c r="EG2" t="n">
-        <v>109.52382</v>
+        <v>1781752553</v>
       </c>
       <c r="EH2" t="n">
-        <v>1756551540</v>
+        <v>1.9999965</v>
       </c>
       <c r="EI2" t="n">
-        <v>1757160000</v>
+        <v>0.204</v>
       </c>
       <c r="EJ2" t="inlineStr"/>
     </row>
